--- a/chart.xlsx
+++ b/chart.xlsx
@@ -818,8 +818,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.28016332093103752"/>
           <c:y val="0.87825541059915646"/>
-          <c:w val="0.43414666079193687"/>
-          <c:h val="6.1211269906643925E-2"/>
+          <c:w val="0.43778132439173029"/>
+          <c:h val="6.0452236685369067E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1014,7 +1014,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{57024E8F-F890-4228-8DA8-6208B59E98FA}" type="CELLRANGE">
+                    <a:fld id="{3D9488F0-220E-426D-9A44-88D3448D59C8}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1022,7 +1022,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{9FF8C5AD-773D-464F-8967-63C6C12A051A}" type="VALUE">
+                    <a:fld id="{ABC27667-2524-4C17-9E60-EF33EC67503B}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -1057,7 +1057,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D4F92B3F-0822-4F33-9354-ECD01836D969}" type="CELLRANGE">
+                    <a:fld id="{9641837D-4E29-43F7-9319-E1825436044F}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1065,7 +1065,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{68969C09-4AFA-40B6-9C59-509E357C97D0}" type="VALUE">
+                    <a:fld id="{8F2E0D3B-58D8-4594-A7A6-C958A027D231}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -1100,7 +1100,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{23FE0885-B3AA-48A5-A71A-D0D704900E8B}" type="CELLRANGE">
+                    <a:fld id="{80C87369-63CC-42C1-995D-94CB882CC855}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1108,7 +1108,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{A4C77DCC-341A-4620-9F78-C4BB6B29C214}" type="VALUE">
+                    <a:fld id="{A12D89B6-9427-40C3-8D0F-DA246F48569C}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -1143,7 +1143,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2B86AF86-E0B3-4202-9EB4-54744AD29545}" type="CELLRANGE">
+                    <a:fld id="{496DCD7D-2EFA-472E-A420-E6311E5A0FAF}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1151,7 +1151,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{0FF63C99-A5D8-46DF-A46D-C145323BE0A5}" type="VALUE">
+                    <a:fld id="{DF6395D4-6844-4291-8037-C2550A5490A1}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -1186,7 +1186,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DDF72C0E-3B97-4CBB-8427-5E1417170D19}" type="CELLRANGE">
+                    <a:fld id="{9AA72419-5637-46D7-A53A-96980343B19D}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1194,7 +1194,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{E7A39BAB-3359-4D85-8993-F58AF4B2BDB9}" type="VALUE">
+                    <a:fld id="{B940F6D7-891B-4601-BAB9-A03DCCF1755D}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -1229,7 +1229,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AA481686-1D4E-40FB-A046-48CB19919B93}" type="CELLRANGE">
+                    <a:fld id="{E9D660D9-48BC-4A1B-933D-0978E8CBF0D1}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1237,7 +1237,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{ED5F9F98-31BA-45F7-817D-D3DC455B29D3}" type="VALUE">
+                    <a:fld id="{150BD3D4-ACBB-4FAB-82FE-C5B2AE11D7C7}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -1272,7 +1272,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6480C515-DE10-45DD-8329-036617404282}" type="CELLRANGE">
+                    <a:fld id="{6152C852-F1E9-4FAD-A86C-8892AA13ACCD}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1280,7 +1280,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{79DEA61A-CEDA-4314-968E-669840106C44}" type="VALUE">
+                    <a:fld id="{7F832B94-83E0-4324-81BC-DE972041D37E}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -1315,7 +1315,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FA1AAA55-EADC-4798-B387-42E25C52FC7F}" type="CELLRANGE">
+                    <a:fld id="{0B2D8FA6-6F35-4DFB-80F5-2D17166459DF}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1323,7 +1323,7 @@
                     <a:endParaRPr lang="en-US" altLang="zh-TW" baseline="0"/>
                   </a:p>
                   <a:p>
-                    <a:fld id="{3AABB86C-913B-49E5-8F64-5925D7640065}" type="VALUE">
+                    <a:fld id="{16340EBE-7FD6-4B28-A98B-CD7C24BB6747}" type="VALUE">
                       <a:rPr lang="en-US" altLang="zh-TW"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
